--- a/解题-gpt/结果/问题三_运输调度_修复版.xlsx
+++ b/解题-gpt/结果/问题三_运输调度_修复版.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="108">
   <si>
     <t>mission_id</t>
   </si>
@@ -79,18 +79,18 @@
     <t>UC01</t>
   </si>
   <si>
+    <t>UC02</t>
+  </si>
+  <si>
+    <t>UA01</t>
+  </si>
+  <si>
     <t>UB01</t>
   </si>
   <si>
-    <t>UA01</t>
-  </si>
-  <si>
     <t>UB02</t>
   </si>
   <si>
-    <t>UC02</t>
-  </si>
-  <si>
     <t>UA02</t>
   </si>
   <si>
@@ -103,54 +103,54 @@
     <t>C</t>
   </si>
   <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>B</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
     <t>C-BAT-01</t>
   </si>
   <si>
+    <t>C-BAT-02</t>
+  </si>
+  <si>
+    <t>C-BAT-03</t>
+  </si>
+  <si>
+    <t>A-BAT-01</t>
+  </si>
+  <si>
     <t>B-BAT-01</t>
   </si>
   <si>
-    <t>A-BAT-01</t>
-  </si>
-  <si>
     <t>B-BAT-02</t>
   </si>
   <si>
+    <t>A-BAT-02</t>
+  </si>
+  <si>
+    <t>A-BAT-03</t>
+  </si>
+  <si>
+    <t>A-BAT-04</t>
+  </si>
+  <si>
+    <t>A-BAT-05</t>
+  </si>
+  <si>
+    <t>A-BAT-06</t>
+  </si>
+  <si>
     <t>B-BAT-03</t>
   </si>
   <si>
+    <t>C-BAT-04</t>
+  </si>
+  <si>
     <t>B-BAT-04</t>
   </si>
   <si>
-    <t>C-BAT-02</t>
-  </si>
-  <si>
-    <t>A-BAT-02</t>
-  </si>
-  <si>
-    <t>C-BAT-03</t>
-  </si>
-  <si>
-    <t>C-BAT-04</t>
-  </si>
-  <si>
-    <t>A-BAT-03</t>
-  </si>
-  <si>
-    <t>A-BAT-04</t>
-  </si>
-  <si>
-    <t>A-BAT-05</t>
-  </si>
-  <si>
-    <t>A-BAT-06</t>
-  </si>
-  <si>
     <t>S001</t>
   </si>
   <si>
@@ -178,12 +178,12 @@
     <t>S003</t>
   </si>
   <si>
+    <t>S008</t>
+  </si>
+  <si>
     <t>S004</t>
   </si>
   <si>
-    <t>S008</t>
-  </si>
-  <si>
     <t>S015</t>
   </si>
   <si>
@@ -199,16 +199,13 @@
     <t>S001-WAT-01,S001-WAT-02,S001-WAT-03,S001-WAT-04,S001-WAT-05,S001-MED-01,S001-MED-02</t>
   </si>
   <si>
+    <t>S002-WAT-01,S002-WAT-02,S002-WAT-03,S002-WAT-04,S002-MED-01</t>
+  </si>
+  <si>
     <t>S001-WAT-06,S001-WAT-07,S001-WAT-08</t>
   </si>
   <si>
-    <t>S002-WAT-01,S002-MED-01</t>
-  </si>
-  <si>
-    <t>S006-WAT-01,S006-WAT-02</t>
-  </si>
-  <si>
-    <t>S006-WAT-03,S006-MED-01</t>
+    <t>S006-WAT-01,S006-MED-01</t>
   </si>
   <si>
     <t>S007-WAT-01,S007-WAT-02</t>
@@ -226,13 +223,10 @@
     <t>S014-WAT-01,S014-MED-01</t>
   </si>
   <si>
-    <t>S002-WAT-02</t>
-  </si>
-  <si>
-    <t>S002-WAT-03</t>
-  </si>
-  <si>
-    <t>S002-WAT-04</t>
+    <t>S006-WAT-02</t>
+  </si>
+  <si>
+    <t>S006-WAT-03</t>
   </si>
   <si>
     <t>S007-MED-01</t>
@@ -241,7 +235,7 @@
     <t>S003-WAT-01,S003-WAT-02,S003-WAT-03,S003-WAT-04,S003-MED-01</t>
   </si>
   <si>
-    <t>S001-FOD-01,S001-FOD-02,S001-FOD-03</t>
+    <t>S008-WAT-01,S008-WAT-02,S008-MED-01</t>
   </si>
   <si>
     <t>S004-WAT-01,S004-WAT-02</t>
@@ -250,18 +244,18 @@
     <t>S004-WAT-03,S004-MED-01</t>
   </si>
   <si>
-    <t>S008-WAT-01,S008-MED-01</t>
+    <t>S001-FOD-01,S001-FOD-02</t>
   </si>
   <si>
     <t>S002-FOD-01,S002-FOD-02</t>
   </si>
   <si>
-    <t>S008-WAT-02</t>
-  </si>
-  <si>
     <t>S015-MED-01</t>
   </si>
   <si>
+    <t>S001-FOD-03</t>
+  </si>
+  <si>
     <t>S006-FOD-01</t>
   </si>
   <si>
@@ -280,7 +274,7 @@
     <t>S014-FOD-01</t>
   </si>
   <si>
-    <t>S005-WAT-01,S005-MED-01</t>
+    <t>S005-WAT-01,S005-WAT-02,S005-WAT-03,S005-MED-01</t>
   </si>
   <si>
     <t>S009-WAT-01,S009-MED-01</t>
@@ -293,12 +287,6 @@
   </si>
   <si>
     <t>S003-FOD-01,S003-FOD-02</t>
-  </si>
-  <si>
-    <t>S005-WAT-02</t>
-  </si>
-  <si>
-    <t>S005-WAT-03</t>
   </si>
   <si>
     <t>S002-HYG-01</t>
@@ -707,7 +695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T50"/>
+  <dimension ref="A1:T46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -828,7 +816,7 @@
         <v>26.19033615606908</v>
       </c>
       <c r="S2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="T2" t="b">
         <v>1</v>
@@ -842,25 +830,25 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
         <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F3" t="s">
         <v>61</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>9.905674851548365</v>
       </c>
       <c r="H3">
-        <v>15.37289355636781</v>
+        <v>33.60645317486046</v>
       </c>
       <c r="I3">
-        <v>20.30834266829118</v>
+        <v>43.96023149817256</v>
       </c>
       <c r="J3">
         <v>60</v>
@@ -869,28 +857,28 @@
         <v>1</v>
       </c>
       <c r="L3">
-        <v>1.063798065282268</v>
+        <v>5.151810515822099</v>
       </c>
       <c r="M3">
-        <v>0.734050483679433</v>
+        <v>0.3560236855222376</v>
       </c>
       <c r="N3">
-        <v>18.79409713814971</v>
+        <v>37.14358913391919</v>
       </c>
       <c r="O3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P3">
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>15.37289355636781</v>
+        <v>23.70077832331209</v>
       </c>
       <c r="R3">
-        <v>20.30834266829118</v>
+        <v>34.05455664662419</v>
       </c>
       <c r="S3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T3" t="b">
         <v>1</v>
@@ -901,28 +889,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
         <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F4" t="s">
         <v>62</v>
       </c>
       <c r="G4">
-        <v>9.905674851548365</v>
+        <v>26.19033615606908</v>
       </c>
       <c r="H4">
-        <v>31.32399636262702</v>
+        <v>42.68858756743695</v>
       </c>
       <c r="I4">
-        <v>43.34431787370568</v>
+        <v>47.98067231213816</v>
       </c>
       <c r="J4">
         <v>60</v>
@@ -931,28 +919,28 @@
         <v>1</v>
       </c>
       <c r="L4">
-        <v>2.421359503464448</v>
+        <v>2.066398756230736</v>
       </c>
       <c r="M4">
-        <v>0.4619201103412338</v>
+        <v>0.741700155471158</v>
       </c>
       <c r="N4">
-        <v>19.9917309426066</v>
+        <v>23.21638327465262</v>
       </c>
       <c r="O4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P4">
-        <v>9.905674851548365</v>
+        <v>26.19033615606908</v>
       </c>
       <c r="Q4">
-        <v>31.32399636262702</v>
+        <v>42.68858756743695</v>
       </c>
       <c r="R4">
-        <v>43.34431787370568</v>
+        <v>47.98067231213816</v>
       </c>
       <c r="S4" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="T4" t="b">
         <v>1</v>
@@ -963,7 +951,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
         <v>29</v>
@@ -981,10 +969,10 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>14.67766295665795</v>
+        <v>15.56128209955562</v>
       </c>
       <c r="I5">
-        <v>20.06321480220478</v>
+        <v>21.83045308800013</v>
       </c>
       <c r="J5">
         <v>60</v>
@@ -993,13 +981,13 @@
         <v>1</v>
       </c>
       <c r="L5">
-        <v>1.087081446911481</v>
+        <v>1.106805665390136</v>
       </c>
       <c r="M5">
-        <v>0.7282296382721298</v>
+        <v>0.7540431854688587</v>
       </c>
       <c r="N5">
-        <v>18.96225489436069</v>
+        <v>13.66239764817473</v>
       </c>
       <c r="O5">
         <v>2</v>
@@ -1008,13 +996,13 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>14.67766295665795</v>
+        <v>15.56128209955562</v>
       </c>
       <c r="R5">
-        <v>20.06321480220478</v>
+        <v>21.83045308800013</v>
       </c>
       <c r="S5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="T5" t="b">
         <v>1</v>
@@ -1028,25 +1016,25 @@
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
         <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F6" t="s">
         <v>64</v>
       </c>
       <c r="G6">
-        <v>20.06321480220478</v>
+        <v>7.323532094892318</v>
       </c>
       <c r="H6">
-        <v>34.74087775886273</v>
+        <v>24.99375750413748</v>
       </c>
       <c r="I6">
-        <v>40.12642960440956</v>
+        <v>33.40931624671596</v>
       </c>
       <c r="J6">
         <v>60</v>
@@ -1055,28 +1043,28 @@
         <v>1</v>
       </c>
       <c r="L6">
-        <v>0.9613264853346692</v>
+        <v>1.60089897336792</v>
       </c>
       <c r="M6">
-        <v>0.7596683786663327</v>
+        <v>0.5997752566580201</v>
       </c>
       <c r="N6">
-        <v>18.05402461630594</v>
+        <v>22.67315925210164</v>
       </c>
       <c r="O6">
         <v>2</v>
       </c>
       <c r="P6">
-        <v>20.06321480220478</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>34.74087775886273</v>
+        <v>17.67022540924516</v>
       </c>
       <c r="R6">
-        <v>40.12642960440956</v>
+        <v>26.08578415182364</v>
       </c>
       <c r="S6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T6" t="b">
         <v>1</v>
@@ -1087,28 +1075,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
         <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F7" t="s">
         <v>65</v>
       </c>
       <c r="G7">
-        <v>20.30834266829118</v>
+        <v>9.905674851548365</v>
       </c>
       <c r="H7">
-        <v>37.97856807753634</v>
+        <v>26.92317826681158</v>
       </c>
       <c r="I7">
-        <v>46.39412682011481</v>
+        <v>34.68945945985256</v>
       </c>
       <c r="J7">
         <v>60</v>
@@ -1117,28 +1105,28 @@
         <v>1</v>
       </c>
       <c r="L7">
-        <v>1.60089897336792</v>
+        <v>1.424415898434041</v>
       </c>
       <c r="M7">
-        <v>0.5997752566580201</v>
+        <v>0.6438960253914898</v>
       </c>
       <c r="N7">
-        <v>22.67315925210164</v>
+        <v>21.39855926646807</v>
       </c>
       <c r="O7">
         <v>2</v>
       </c>
       <c r="P7">
-        <v>20.30834266829118</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>37.97856807753634</v>
+        <v>17.01750341526321</v>
       </c>
       <c r="R7">
-        <v>46.39412682011481</v>
+        <v>24.7837846083042</v>
       </c>
       <c r="S7" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="T7" t="b">
         <v>1</v>
@@ -1149,16 +1137,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
         <v>37</v>
       </c>
       <c r="E8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F8" t="s">
         <v>66</v>
@@ -1167,10 +1155,10 @@
         <v>9.905674851548365</v>
       </c>
       <c r="H8">
-        <v>28.09110245175328</v>
+        <v>27.9464117111378</v>
       </c>
       <c r="I8">
-        <v>36.44969671862485</v>
+        <v>36.73603745961613</v>
       </c>
       <c r="J8">
         <v>60</v>
@@ -1179,28 +1167,28 @@
         <v>1</v>
       </c>
       <c r="L8">
-        <v>2.910315433999106</v>
+        <v>1.637365079674389</v>
       </c>
       <c r="M8">
-        <v>0.6362105707501118</v>
+        <v>0.6361410934056912</v>
       </c>
       <c r="N8">
-        <v>27.0257293895793</v>
+        <v>16.21694297621002</v>
       </c>
       <c r="O8">
         <v>2</v>
       </c>
       <c r="P8">
-        <v>9.905674851548365</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>28.09110245175328</v>
+        <v>18.04073685958943</v>
       </c>
       <c r="R8">
-        <v>36.44969671862485</v>
+        <v>26.83036260806776</v>
       </c>
       <c r="S8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="T8" t="b">
         <v>1</v>
@@ -1211,16 +1199,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
         <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F9" t="s">
         <v>67</v>
@@ -1229,10 +1217,10 @@
         <v>9.905674851548365</v>
       </c>
       <c r="H9">
-        <v>27.9464117111378</v>
+        <v>32.14420882468487</v>
       </c>
       <c r="I9">
-        <v>36.73603745961613</v>
+        <v>45.05174279782136</v>
       </c>
       <c r="J9">
         <v>60</v>
@@ -1241,28 +1229,28 @@
         <v>1</v>
       </c>
       <c r="L9">
-        <v>1.637365079674389</v>
+        <v>2.471325003399136</v>
       </c>
       <c r="M9">
-        <v>0.6361410934056912</v>
+        <v>0.4508166659113031</v>
       </c>
       <c r="N9">
-        <v>16.21694297621002</v>
+        <v>20.23230557192176</v>
       </c>
       <c r="O9">
         <v>2</v>
       </c>
       <c r="P9">
-        <v>9.905674851548365</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>27.9464117111378</v>
+        <v>22.2385339731365</v>
       </c>
       <c r="R9">
-        <v>36.73603745961613</v>
+        <v>35.146067946273</v>
       </c>
       <c r="S9" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="T9" t="b">
         <v>1</v>
@@ -1273,28 +1261,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
         <v>39</v>
       </c>
       <c r="E10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F10" t="s">
         <v>68</v>
       </c>
       <c r="G10">
-        <v>26.19033615606908</v>
+        <v>9.905674851548365</v>
       </c>
       <c r="H10">
-        <v>47.61045803875672</v>
+        <v>31.12234688112371</v>
       </c>
       <c r="I10">
-        <v>59.08407992144435</v>
+        <v>43.0871300218102</v>
       </c>
       <c r="J10">
         <v>60</v>
@@ -1303,28 +1291,28 @@
         <v>1</v>
       </c>
       <c r="L10">
-        <v>4.320888294761101</v>
+        <v>1.974536954059142</v>
       </c>
       <c r="M10">
-        <v>0.4598889631548624</v>
+        <v>0.5612140102090795</v>
       </c>
       <c r="N10">
-        <v>33.39289855274107</v>
+        <v>17.84036311213661</v>
       </c>
       <c r="O10">
         <v>2</v>
       </c>
       <c r="P10">
-        <v>26.19033615606908</v>
+        <v>0</v>
       </c>
       <c r="Q10">
-        <v>47.61045803875672</v>
+        <v>21.21667202957535</v>
       </c>
       <c r="R10">
-        <v>59.08407992144435</v>
+        <v>33.18145517026183</v>
       </c>
       <c r="S10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="T10" t="b">
         <v>1</v>
@@ -1335,28 +1323,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
         <v>40</v>
       </c>
       <c r="E11" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F11" t="s">
         <v>69</v>
       </c>
       <c r="G11">
-        <v>36.44969671862485</v>
+        <v>21.83045308800013</v>
       </c>
       <c r="H11">
-        <v>57.78439582356296</v>
+        <v>36.39173518755575</v>
       </c>
       <c r="I11">
-        <v>69.29126159516773</v>
+        <v>42.66090617600025</v>
       </c>
       <c r="J11">
         <v>60</v>
@@ -1365,28 +1353,28 @@
         <v>1</v>
       </c>
       <c r="L11">
-        <v>3.58861224407448</v>
+        <v>1.092476706316119</v>
       </c>
       <c r="M11">
-        <v>0.55142346949069</v>
+        <v>0.757227398596418</v>
       </c>
       <c r="N11">
-        <v>30.0874858239473</v>
+        <v>13.59340636374428</v>
       </c>
       <c r="O11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P11">
-        <v>9.905674851548365</v>
+        <v>21.83045308800013</v>
       </c>
       <c r="Q11">
-        <v>31.24037395648647</v>
+        <v>36.39173518755575</v>
       </c>
       <c r="R11">
-        <v>42.74723972809124</v>
+        <v>42.66090617600025</v>
       </c>
       <c r="S11" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="T11" t="b">
         <v>1</v>
@@ -1397,28 +1385,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s">
         <v>41</v>
       </c>
       <c r="E12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F12" t="s">
         <v>70</v>
       </c>
       <c r="G12">
-        <v>9.905674851548365</v>
+        <v>36.73603745961613</v>
       </c>
       <c r="H12">
-        <v>30.32399636262702</v>
+        <v>51.29731955917176</v>
       </c>
       <c r="I12">
-        <v>42.34431787370568</v>
+        <v>57.56649054761626</v>
       </c>
       <c r="J12">
         <v>60</v>
@@ -1427,28 +1415,28 @@
         <v>1</v>
       </c>
       <c r="L12">
-        <v>2.38786730414774</v>
+        <v>1.092476706316119</v>
       </c>
       <c r="M12">
-        <v>0.4693628213005021</v>
+        <v>0.757227398596418</v>
       </c>
       <c r="N12">
-        <v>19.83047220515579</v>
+        <v>13.59340636374428</v>
       </c>
       <c r="O12">
         <v>1</v>
       </c>
       <c r="P12">
-        <v>9.905674851548365</v>
+        <v>26.83036260806776</v>
       </c>
       <c r="Q12">
-        <v>30.32399636262702</v>
+        <v>41.39164470762339</v>
       </c>
       <c r="R12">
-        <v>42.34431787370568</v>
+        <v>47.66081569606789</v>
       </c>
       <c r="S12" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="T12" t="b">
         <v>1</v>
@@ -1459,7 +1447,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
         <v>30</v>
@@ -1468,19 +1456,19 @@
         <v>42</v>
       </c>
       <c r="E13" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F13" t="s">
         <v>71</v>
       </c>
       <c r="G13">
-        <v>9.905674851548365</v>
+        <v>33.40931624671596</v>
       </c>
       <c r="H13">
-        <v>30.32399636262702</v>
+        <v>50.07954165596111</v>
       </c>
       <c r="I13">
-        <v>42.34431787370568</v>
+        <v>58.49510039853959</v>
       </c>
       <c r="J13">
         <v>60</v>
@@ -1489,28 +1477,28 @@
         <v>1</v>
       </c>
       <c r="L13">
-        <v>2.38786730414774</v>
+        <v>1.278665737006417</v>
       </c>
       <c r="M13">
-        <v>0.4693628213005021</v>
+        <v>0.6803335657483958</v>
       </c>
       <c r="N13">
-        <v>19.83047220515579</v>
+        <v>20.34591921171301</v>
       </c>
       <c r="O13">
         <v>1</v>
       </c>
       <c r="P13">
-        <v>36.73603745961613</v>
+        <v>24.7837846083042</v>
       </c>
       <c r="Q13">
-        <v>57.15435897069479</v>
+        <v>41.45401001754935</v>
       </c>
       <c r="R13">
-        <v>69.17468048177344</v>
+        <v>49.86956876012783</v>
       </c>
       <c r="S13" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="T13" t="b">
         <v>1</v>
@@ -1521,58 +1509,58 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s">
         <v>43</v>
       </c>
       <c r="E14" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F14" t="s">
         <v>72</v>
       </c>
       <c r="G14">
-        <v>36.73603745961613</v>
+        <v>43.96023149817256</v>
       </c>
       <c r="H14">
-        <v>57.15435897069479</v>
+        <v>70.20848545797438</v>
       </c>
       <c r="I14">
-        <v>69.17468048177344</v>
+        <v>83.30807275110952</v>
       </c>
       <c r="J14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="K14" t="b">
         <v>1</v>
       </c>
       <c r="L14">
-        <v>2.38786730414774</v>
+        <v>5.440500810633867</v>
       </c>
       <c r="M14">
-        <v>0.4693628213005021</v>
+        <v>0.3199373986707666</v>
       </c>
       <c r="N14">
-        <v>19.83047220515579</v>
+        <v>38.44670504800009</v>
       </c>
       <c r="O14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P14">
-        <v>42.34431787370568</v>
+        <v>34.05455664662419</v>
       </c>
       <c r="Q14">
-        <v>62.76263938478434</v>
+        <v>60.30281060642601</v>
       </c>
       <c r="R14">
-        <v>74.78296089586298</v>
+        <v>73.40239789956115</v>
       </c>
       <c r="S14" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="T14" t="b">
         <v>1</v>
@@ -1583,58 +1571,58 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E15" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F15" t="s">
         <v>73</v>
       </c>
       <c r="G15">
-        <v>40.12642960440956</v>
+        <v>51.62987554632826</v>
       </c>
       <c r="H15">
-        <v>56.79665501365471</v>
+        <v>74.37264188394303</v>
       </c>
       <c r="I15">
-        <v>65.21221375623318</v>
+        <v>86.05407488822445</v>
       </c>
       <c r="J15">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
       </c>
       <c r="L15">
-        <v>1.278665737006417</v>
+        <v>4.880456740806956</v>
       </c>
       <c r="M15">
-        <v>0.6803335657483958</v>
+        <v>0.3899429073991305</v>
       </c>
       <c r="N15">
-        <v>20.34591921171301</v>
+        <v>35.91872834392029</v>
       </c>
       <c r="O15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P15">
-        <v>40.12642960440956</v>
+        <v>51.62987554632827</v>
       </c>
       <c r="Q15">
-        <v>56.79665501365471</v>
+        <v>74.37264188394303</v>
       </c>
       <c r="R15">
-        <v>65.21221375623318</v>
+        <v>86.05407488822445</v>
       </c>
       <c r="S15" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="T15" t="b">
         <v>1</v>
@@ -1645,28 +1633,28 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="E16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F16" t="s">
         <v>74</v>
       </c>
       <c r="G16">
-        <v>59.08407992144435</v>
+        <v>34.68945945985256</v>
       </c>
       <c r="H16">
-        <v>85.33233388124617</v>
+        <v>55.50706608529354</v>
       </c>
       <c r="I16">
-        <v>98.4319211743813</v>
+        <v>66.93645048851229</v>
       </c>
       <c r="J16">
         <v>120</v>
@@ -1675,28 +1663,28 @@
         <v>1</v>
       </c>
       <c r="L16">
-        <v>5.440500810633867</v>
+        <v>2.546881484042609</v>
       </c>
       <c r="M16">
-        <v>0.3199373986707666</v>
+        <v>0.3632796289893477</v>
       </c>
       <c r="N16">
-        <v>38.44670504800009</v>
+        <v>29.50525516252995</v>
       </c>
       <c r="O16">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P16">
-        <v>36.44969671862485</v>
+        <v>26.08578415182364</v>
       </c>
       <c r="Q16">
-        <v>62.69795067842667</v>
+        <v>46.90339077726461</v>
       </c>
       <c r="R16">
-        <v>75.79753797156181</v>
+        <v>58.33277518048336</v>
       </c>
       <c r="S16" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="T16" t="b">
         <v>1</v>
@@ -1707,28 +1695,28 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E17" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="F17" t="s">
         <v>75</v>
       </c>
       <c r="G17">
-        <v>69.29126159516773</v>
+        <v>58.49510039853959</v>
       </c>
       <c r="H17">
-        <v>85.7895130065356</v>
+        <v>79.31270702398058</v>
       </c>
       <c r="I17">
-        <v>91.08159775123681</v>
+        <v>90.74209142719931</v>
       </c>
       <c r="J17">
         <v>120</v>
@@ -1737,28 +1725,28 @@
         <v>1</v>
       </c>
       <c r="L17">
-        <v>1.914498008428869</v>
+        <v>2.240674227365981</v>
       </c>
       <c r="M17">
-        <v>0.7606877489463914</v>
+        <v>0.4398314431585046</v>
       </c>
       <c r="N17">
-        <v>22.53072017693587</v>
+        <v>27.29375830875431</v>
       </c>
       <c r="O17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P17">
-        <v>59.08407992144435</v>
+        <v>49.86956876012783</v>
       </c>
       <c r="Q17">
-        <v>75.58233133281222</v>
+        <v>70.68717538556881</v>
       </c>
       <c r="R17">
-        <v>80.87441607751343</v>
+        <v>82.11655978878755</v>
       </c>
       <c r="S17" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T17" t="b">
         <v>1</v>
@@ -1769,28 +1757,28 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C18" t="s">
         <v>29</v>
       </c>
       <c r="D18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
         <v>76</v>
       </c>
       <c r="G18">
-        <v>46.39412682011481</v>
+        <v>42.66090617600025</v>
       </c>
       <c r="H18">
-        <v>67.21173344555578</v>
+        <v>57.88474614762662</v>
       </c>
       <c r="I18">
-        <v>78.64111784877454</v>
+        <v>63.67114167480854</v>
       </c>
       <c r="J18">
         <v>120</v>
@@ -1799,28 +1787,28 @@
         <v>1</v>
       </c>
       <c r="L18">
-        <v>2.546881484042609</v>
+        <v>1.048835444247772</v>
       </c>
       <c r="M18">
-        <v>0.3632796289893477</v>
+        <v>0.7669254568338284</v>
       </c>
       <c r="N18">
-        <v>29.50525516252995</v>
+        <v>13.38328176860038</v>
       </c>
       <c r="O18">
         <v>2</v>
       </c>
       <c r="P18">
-        <v>46.39412682011481</v>
+        <v>35.49285073617485</v>
       </c>
       <c r="Q18">
-        <v>67.21173344555578</v>
+        <v>50.71669070780122</v>
       </c>
       <c r="R18">
-        <v>78.64111784877454</v>
+        <v>56.50308623498314</v>
       </c>
       <c r="S18" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="T18" t="b">
         <v>1</v>
@@ -1831,28 +1819,28 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
         <v>29</v>
       </c>
       <c r="D19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E19" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
         <v>77</v>
       </c>
       <c r="G19">
-        <v>65.21221375623318</v>
+        <v>52.95298043582615</v>
       </c>
       <c r="H19">
-        <v>86.02982038167417</v>
+        <v>74.37130194690481</v>
       </c>
       <c r="I19">
-        <v>97.4592047848929</v>
+        <v>86.39162345798346</v>
       </c>
       <c r="J19">
         <v>120</v>
@@ -1861,28 +1849,28 @@
         <v>1</v>
       </c>
       <c r="L19">
-        <v>2.240674227365981</v>
+        <v>2.409990591769786</v>
       </c>
       <c r="M19">
-        <v>0.4398314431585046</v>
+        <v>0.4644465351622699</v>
       </c>
       <c r="N19">
-        <v>27.29375830875431</v>
+        <v>19.93699173815082</v>
       </c>
       <c r="O19">
         <v>2</v>
       </c>
       <c r="P19">
-        <v>65.21221375623318</v>
+        <v>43.04730558427778</v>
       </c>
       <c r="Q19">
-        <v>86.02982038167417</v>
+        <v>64.46562709535644</v>
       </c>
       <c r="R19">
-        <v>97.4592047848929</v>
+        <v>76.48594860643509</v>
       </c>
       <c r="S19" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="T19" t="b">
         <v>1</v>
@@ -1896,25 +1884,25 @@
         <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F20" t="s">
         <v>78</v>
       </c>
       <c r="G20">
-        <v>42.34431787370568</v>
+        <v>56.25431253974453</v>
       </c>
       <c r="H20">
-        <v>65.10697432608441</v>
+        <v>76.19365451958166</v>
       </c>
       <c r="I20">
-        <v>78.52874188957426</v>
+        <v>88.0183298327521</v>
       </c>
       <c r="J20">
         <v>120</v>
@@ -1923,28 +1911,28 @@
         <v>1</v>
       </c>
       <c r="L20">
-        <v>2.660432042052936</v>
+        <v>1.976874086653691</v>
       </c>
       <c r="M20">
-        <v>0.408792879543792</v>
+        <v>0.5606946474102907</v>
       </c>
       <c r="N20">
-        <v>21.14282094321784</v>
+        <v>17.85161597277703</v>
       </c>
       <c r="O20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P20">
-        <v>52.95298043582615</v>
+        <v>51.02181828239844</v>
       </c>
       <c r="Q20">
-        <v>75.71563688820488</v>
+        <v>70.96116026223557</v>
       </c>
       <c r="R20">
-        <v>89.13740445169474</v>
+        <v>82.78583557540601</v>
       </c>
       <c r="S20" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="T20" t="b">
         <v>1</v>
@@ -1955,28 +1943,28 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F21" t="s">
         <v>79</v>
       </c>
       <c r="G21">
-        <v>52.95298043582615</v>
+        <v>60.92749313394681</v>
       </c>
       <c r="H21">
-        <v>74.37130194690481</v>
+        <v>75.15133310557317</v>
       </c>
       <c r="I21">
-        <v>86.39162345798346</v>
+        <v>80.93772863275511</v>
       </c>
       <c r="J21">
         <v>120</v>
@@ -1985,28 +1973,28 @@
         <v>1</v>
       </c>
       <c r="L21">
-        <v>2.409990591769786</v>
+        <v>1.014245103020607</v>
       </c>
       <c r="M21">
-        <v>0.4644465351622699</v>
+        <v>0.7746121993287539</v>
       </c>
       <c r="N21">
-        <v>19.93699173815082</v>
+        <v>13.21673568121033</v>
       </c>
       <c r="O21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P21">
-        <v>60.92749313394681</v>
+        <v>55.37837351819476</v>
       </c>
       <c r="Q21">
-        <v>82.34581464502547</v>
+        <v>69.60221348982112</v>
       </c>
       <c r="R21">
-        <v>94.36613615610412</v>
+        <v>75.38860901700306</v>
       </c>
       <c r="S21" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="T21" t="b">
         <v>1</v>
@@ -2020,25 +2008,25 @@
         <v>22</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D22" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E22" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F22" t="s">
         <v>80</v>
       </c>
       <c r="G22">
-        <v>62.17479007886146</v>
+        <v>65.28404836974312</v>
       </c>
       <c r="H22">
-        <v>83.9374465312402</v>
+        <v>79.84533046929874</v>
       </c>
       <c r="I22">
-        <v>97.35921409473004</v>
+        <v>86.11450145774324</v>
       </c>
       <c r="J22">
         <v>120</v>
@@ -2047,28 +2035,28 @@
         <v>1</v>
       </c>
       <c r="L22">
-        <v>2.623902934018422</v>
+        <v>1.066023243410243</v>
       </c>
       <c r="M22">
-        <v>0.4169104591070174</v>
+        <v>0.7631059459088348</v>
       </c>
       <c r="N22">
-        <v>20.96694005268129</v>
+        <v>13.46603783864191</v>
       </c>
       <c r="O22">
         <v>1</v>
       </c>
       <c r="P22">
-        <v>69.17468048177344</v>
+        <v>56.50308623498314</v>
       </c>
       <c r="Q22">
-        <v>90.93733693415217</v>
+        <v>71.06436833453876</v>
       </c>
       <c r="R22">
-        <v>104.359104497642</v>
+        <v>77.33353932298327</v>
       </c>
       <c r="S22" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="T22" t="b">
         <v>1</v>
@@ -2079,28 +2067,28 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C23" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D23" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E23" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F23" t="s">
         <v>81</v>
       </c>
       <c r="G23">
-        <v>92.47697847418542</v>
+        <v>80.93772863275511</v>
       </c>
       <c r="H23">
-        <v>111.9916814491121</v>
+        <v>98.86734894077981</v>
       </c>
       <c r="I23">
-        <v>122.9843844240387</v>
+        <v>108.5423025821379</v>
       </c>
       <c r="J23">
         <v>120</v>
@@ -2109,28 +2097,28 @@
         <v>1</v>
       </c>
       <c r="L23">
-        <v>3.56316577275202</v>
+        <v>1.571297495086422</v>
       </c>
       <c r="M23">
-        <v>0.5546042784059975</v>
+        <v>0.6508227788696839</v>
       </c>
       <c r="N23">
-        <v>29.97262327978342</v>
+        <v>15.89883979115685</v>
       </c>
       <c r="O23">
         <v>1</v>
       </c>
       <c r="P23">
-        <v>75.79753797156181</v>
+        <v>75.38860901700306</v>
       </c>
       <c r="Q23">
-        <v>95.31224094648847</v>
+        <v>93.31822932502776</v>
       </c>
       <c r="R23">
-        <v>106.3049439214151</v>
+        <v>102.9931829663858</v>
       </c>
       <c r="S23" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="T23" t="b">
         <v>1</v>
@@ -2141,28 +2129,28 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D24" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E24" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F24" t="s">
         <v>82</v>
       </c>
       <c r="G24">
-        <v>69.17468048177344</v>
+        <v>86.11450145774324</v>
       </c>
       <c r="H24">
-        <v>83.73596258132906</v>
+        <v>103.4593474567197</v>
       </c>
       <c r="I24">
-        <v>90.00513356977356</v>
+        <v>112.552971233474</v>
       </c>
       <c r="J24">
         <v>120</v>
@@ -2171,28 +2159,28 @@
         <v>1</v>
       </c>
       <c r="L24">
-        <v>1.066023243410243</v>
+        <v>1.581530554767664</v>
       </c>
       <c r="M24">
-        <v>0.7631059459088348</v>
+        <v>0.6485487656071858</v>
       </c>
       <c r="N24">
-        <v>13.46603783864191</v>
+        <v>15.94811007851097</v>
       </c>
       <c r="O24">
         <v>1</v>
       </c>
       <c r="P24">
-        <v>74.78296089586298</v>
+        <v>76.48594860643509</v>
       </c>
       <c r="Q24">
-        <v>89.34424299541861</v>
+        <v>93.83079460541157</v>
       </c>
       <c r="R24">
-        <v>95.61341398386311</v>
+        <v>102.9244183821658</v>
       </c>
       <c r="S24" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T24" t="b">
         <v>1</v>
@@ -2203,28 +2191,28 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C25" t="s">
         <v>30</v>
       </c>
       <c r="D25" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E25" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F25" t="s">
         <v>83</v>
       </c>
       <c r="G25">
-        <v>78.52874188957426</v>
+        <v>66.93645048851229</v>
       </c>
       <c r="H25">
-        <v>96.45836219759896</v>
+        <v>86.11986242216884</v>
       </c>
       <c r="I25">
-        <v>106.133315838957</v>
+        <v>96.97227435582539</v>
       </c>
       <c r="J25">
         <v>120</v>
@@ -2233,28 +2221,28 @@
         <v>1</v>
       </c>
       <c r="L25">
-        <v>1.571297495086422</v>
+        <v>1.971677737898548</v>
       </c>
       <c r="M25">
-        <v>0.6508227788696839</v>
+        <v>0.5070805655253631</v>
       </c>
       <c r="N25">
-        <v>15.89883979115685</v>
+        <v>25.35100588482284</v>
       </c>
       <c r="O25">
         <v>1</v>
       </c>
       <c r="P25">
-        <v>89.13740445169474</v>
+        <v>58.33277518048336</v>
       </c>
       <c r="Q25">
-        <v>107.0670247597194</v>
+        <v>77.51618711413991</v>
       </c>
       <c r="R25">
-        <v>116.7419784010775</v>
+        <v>88.36859904779647</v>
       </c>
       <c r="S25" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="T25" t="b">
         <v>1</v>
@@ -2268,25 +2256,25 @@
         <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D26" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F26" t="s">
         <v>84</v>
       </c>
       <c r="G26">
-        <v>89.00515268692922</v>
+        <v>94.15446431396543</v>
       </c>
       <c r="H26">
-        <v>106.3499986859057</v>
+        <v>111.1952011735548</v>
       </c>
       <c r="I26">
-        <v>115.4436224626599</v>
+        <v>119.9848269220332</v>
       </c>
       <c r="J26">
         <v>120</v>
@@ -2295,28 +2283,28 @@
         <v>1</v>
       </c>
       <c r="L26">
-        <v>1.581530554767664</v>
+        <v>1.575202255282084</v>
       </c>
       <c r="M26">
-        <v>0.6485487656071858</v>
+        <v>0.6499550543817592</v>
       </c>
       <c r="N26">
-        <v>15.94811007851097</v>
+        <v>15.91764048839522</v>
       </c>
       <c r="O26">
         <v>1</v>
       </c>
       <c r="P26">
-        <v>94.61343310101877</v>
+        <v>88.6053446982134</v>
       </c>
       <c r="Q26">
-        <v>111.9582790999953</v>
+        <v>105.6460815578028</v>
       </c>
       <c r="R26">
-        <v>121.0519028767495</v>
+        <v>114.4357073062812</v>
       </c>
       <c r="S26" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="T26" t="b">
         <v>1</v>
@@ -2327,28 +2315,28 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D27" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F27" t="s">
         <v>85</v>
       </c>
       <c r="G27">
-        <v>78.64111784877454</v>
+        <v>90.74209142719931</v>
       </c>
       <c r="H27">
-        <v>97.8245297824311</v>
+        <v>109.4557330066351</v>
       </c>
       <c r="I27">
-        <v>108.6769417160876</v>
+        <v>119.9174856971819</v>
       </c>
       <c r="J27">
         <v>120</v>
@@ -2357,28 +2345,28 @@
         <v>1</v>
       </c>
       <c r="L27">
-        <v>1.971677737898548</v>
+        <v>1.607789512414177</v>
       </c>
       <c r="M27">
-        <v>0.5070805655253631</v>
+        <v>0.5980526218964557</v>
       </c>
       <c r="N27">
-        <v>25.35100588482284</v>
+        <v>22.72292425632461</v>
       </c>
       <c r="O27">
         <v>1</v>
       </c>
       <c r="P27">
-        <v>78.64111784877454</v>
+        <v>82.11655978878755</v>
       </c>
       <c r="Q27">
-        <v>97.8245297824311</v>
+        <v>100.8302013682233</v>
       </c>
       <c r="R27">
-        <v>108.6769417160876</v>
+        <v>111.2919540587701</v>
       </c>
       <c r="S27" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="T27" t="b">
         <v>1</v>
@@ -2389,58 +2377,58 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E28" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="F28" t="s">
         <v>86</v>
       </c>
       <c r="G28">
-        <v>97.4592047848929</v>
+        <v>83.30807275110952</v>
       </c>
       <c r="H28">
-        <v>113.1530804493157</v>
+        <v>103.944024092142</v>
       </c>
       <c r="I28">
-        <v>120.5958450026275</v>
+        <v>112.2921420998412</v>
       </c>
       <c r="J28">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="K28" t="b">
         <v>1</v>
       </c>
       <c r="L28">
-        <v>1.309771480726076</v>
+        <v>3.517681856451785</v>
       </c>
       <c r="M28">
-        <v>0.672557129818481</v>
+        <v>0.5602897679435269</v>
       </c>
       <c r="N28">
-        <v>20.57057180524388</v>
+        <v>29.76731393537263</v>
       </c>
       <c r="O28">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P28">
-        <v>97.4592047848929</v>
+        <v>73.40239789956115</v>
       </c>
       <c r="Q28">
-        <v>113.1530804493157</v>
+        <v>94.03834924059366</v>
       </c>
       <c r="R28">
-        <v>120.5958450026275</v>
+        <v>102.3864672482928</v>
       </c>
       <c r="S28" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="T28" t="b">
         <v>1</v>
@@ -2451,58 +2439,58 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C29" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D29" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E29" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F29" t="s">
         <v>87</v>
       </c>
       <c r="G29">
-        <v>99.37874741911503</v>
+        <v>99.58053929638515</v>
       </c>
       <c r="H29">
-        <v>119.6134465240531</v>
+        <v>118.3453744515041</v>
       </c>
       <c r="I29">
-        <v>131.1203122956579</v>
+        <v>127.7238762732897</v>
       </c>
       <c r="J29">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="K29" t="b">
         <v>1</v>
       </c>
       <c r="L29">
-        <v>3.492318945036377</v>
+        <v>1.8710546231918</v>
       </c>
       <c r="M29">
-        <v>0.5634601318704529</v>
+        <v>0.5842100837351556</v>
       </c>
       <c r="N29">
-        <v>29.65282857134476</v>
+        <v>17.34211485240496</v>
       </c>
       <c r="O29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P29">
-        <v>92.47697847418542</v>
+        <v>90.79957716162518</v>
       </c>
       <c r="Q29">
-        <v>112.7116775791235</v>
+        <v>109.5644123167441</v>
       </c>
       <c r="R29">
-        <v>124.2185433507283</v>
+        <v>118.9429141385297</v>
       </c>
       <c r="S29" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="T29" t="b">
         <v>1</v>
@@ -2516,25 +2504,25 @@
         <v>25</v>
       </c>
       <c r="C30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E30" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F30" t="s">
         <v>88</v>
       </c>
       <c r="G30">
-        <v>99.67156283279211</v>
+        <v>108.5423025821379</v>
       </c>
       <c r="H30">
-        <v>118.4543771143929</v>
+        <v>123.3749793107571</v>
       </c>
       <c r="I30">
-        <v>127.8119691737715</v>
+        <v>128.801433817154</v>
       </c>
       <c r="J30">
         <v>180</v>
@@ -2543,28 +2531,28 @@
         <v>1</v>
       </c>
       <c r="L30">
-        <v>1.779919328040352</v>
+        <v>0.974739867166567</v>
       </c>
       <c r="M30">
-        <v>0.6044623715465884</v>
+        <v>0.7833911406296518</v>
       </c>
       <c r="N30">
-        <v>16.90331528315725</v>
+        <v>13.02652528635754</v>
       </c>
       <c r="O30">
         <v>2</v>
       </c>
       <c r="P30">
-        <v>109.079451822505</v>
+        <v>102.9244183821658</v>
       </c>
       <c r="Q30">
-        <v>127.8622661041058</v>
+        <v>117.757095110785</v>
       </c>
       <c r="R30">
-        <v>137.2198581634844</v>
+        <v>123.1835496171819</v>
       </c>
       <c r="S30" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="T30" t="b">
         <v>1</v>
@@ -2575,28 +2563,28 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C31" t="s">
         <v>30</v>
       </c>
       <c r="D31" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E31" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="F31" t="s">
         <v>89</v>
       </c>
       <c r="G31">
-        <v>103.4711714084155</v>
+        <v>96.97227435582539</v>
       </c>
       <c r="H31">
-        <v>122.2360065635344</v>
+        <v>111.3451679121932</v>
       </c>
       <c r="I31">
-        <v>131.61450838532</v>
+        <v>116.2806170241165</v>
       </c>
       <c r="J31">
         <v>180</v>
@@ -2605,28 +2593,28 @@
         <v>1</v>
       </c>
       <c r="L31">
-        <v>1.8710546231918</v>
+        <v>0.8736555559417358</v>
       </c>
       <c r="M31">
-        <v>0.5842100837351556</v>
+        <v>0.7815861110145661</v>
       </c>
       <c r="N31">
-        <v>17.34211485240496</v>
+        <v>17.42084568180142</v>
       </c>
       <c r="O31">
         <v>2</v>
       </c>
       <c r="P31">
-        <v>110.2802253949126</v>
+        <v>88.36859904779647</v>
       </c>
       <c r="Q31">
-        <v>129.0450605500315</v>
+        <v>102.7414926041643</v>
       </c>
       <c r="R31">
-        <v>138.4235623718171</v>
+        <v>107.6769417160876</v>
       </c>
       <c r="S31" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="T31" t="b">
         <v>1</v>
@@ -2637,28 +2625,28 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D32" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E32" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F32" t="s">
         <v>90</v>
       </c>
       <c r="G32">
-        <v>108.6769417160876</v>
+        <v>118.0358497359536</v>
       </c>
       <c r="H32">
-        <v>122.7270773797231</v>
+        <v>139.4433870243834</v>
       </c>
       <c r="I32">
-        <v>127.3709908211363</v>
+        <v>151.5851465350355</v>
       </c>
       <c r="J32">
         <v>180</v>
@@ -2667,28 +2655,28 @@
         <v>1</v>
       </c>
       <c r="L32">
-        <v>0.845945507122666</v>
+        <v>2.171939602406073</v>
       </c>
       <c r="M32">
-        <v>0.7885136232193335</v>
+        <v>0.4570150993984818</v>
       </c>
       <c r="N32">
-        <v>17.22071755144147</v>
+        <v>26.79734157293274</v>
       </c>
       <c r="O32">
         <v>2</v>
       </c>
       <c r="P32">
-        <v>108.6769417160876</v>
+        <v>109.4103180975419</v>
       </c>
       <c r="Q32">
-        <v>122.7270773797231</v>
+        <v>130.8178553859717</v>
       </c>
       <c r="R32">
-        <v>127.3709908211363</v>
+        <v>142.9596148966238</v>
       </c>
       <c r="S32" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T32" t="b">
         <v>1</v>
@@ -2699,28 +2687,28 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C33" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D33" t="s">
         <v>37</v>
       </c>
       <c r="E33" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F33" t="s">
         <v>91</v>
       </c>
       <c r="G33">
-        <v>122.9843844240387</v>
+        <v>112.552971233474</v>
       </c>
       <c r="H33">
-        <v>138.3826358354066</v>
+        <v>132.9712927445526</v>
       </c>
       <c r="I33">
-        <v>143.6747205801078</v>
+        <v>144.9916142556312</v>
       </c>
       <c r="J33">
         <v>180</v>
@@ -2729,28 +2717,28 @@
         <v>1</v>
       </c>
       <c r="L33">
-        <v>1.835475722612836</v>
+        <v>2.306810552860246</v>
       </c>
       <c r="M33">
-        <v>0.7705655346733955</v>
+        <v>0.4873754326977231</v>
       </c>
       <c r="N33">
-        <v>22.17402235901627</v>
+        <v>19.440198958216</v>
       </c>
       <c r="O33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P33">
-        <v>106.3049439214151</v>
+        <v>102.9931829663858</v>
       </c>
       <c r="Q33">
-        <v>121.703195332783</v>
+        <v>123.4115044774644</v>
       </c>
       <c r="R33">
-        <v>126.9952800774842</v>
+        <v>135.4318259885431</v>
       </c>
       <c r="S33" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T33" t="b">
         <v>1</v>
@@ -2761,28 +2749,28 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D34" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E34" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F34" t="s">
         <v>92</v>
       </c>
       <c r="G34">
-        <v>124.7529630936472</v>
+        <v>86.05407488822445</v>
       </c>
       <c r="H34">
-        <v>146.1605003820771</v>
+        <v>107.0726497510757</v>
       </c>
       <c r="I34">
-        <v>158.3022598927292</v>
+        <v>119.1588912805937</v>
       </c>
       <c r="J34">
         <v>180</v>
@@ -2791,28 +2779,28 @@
         <v>1</v>
       </c>
       <c r="L34">
-        <v>2.171939602406073</v>
+        <v>4.403269646749423</v>
       </c>
       <c r="M34">
-        <v>0.4570150993984818</v>
+        <v>0.4495912941563222</v>
       </c>
       <c r="N34">
-        <v>26.79734157293274</v>
+        <v>33.7647588221328</v>
       </c>
       <c r="O34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P34">
-        <v>124.7529630936472</v>
+        <v>86.05407488822445</v>
       </c>
       <c r="Q34">
-        <v>146.1605003820771</v>
+        <v>107.0726497510757</v>
       </c>
       <c r="R34">
-        <v>158.3022598927292</v>
+        <v>119.1588912805937</v>
       </c>
       <c r="S34" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="T34" t="b">
         <v>1</v>
@@ -2823,28 +2811,28 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D35" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E35" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F35" t="s">
         <v>93</v>
       </c>
       <c r="G35">
-        <v>106.3286151961343</v>
+        <v>124.4411423732947</v>
       </c>
       <c r="H35">
-        <v>124.111429477735</v>
+        <v>139.0024244728503</v>
       </c>
       <c r="I35">
-        <v>133.4690215371136</v>
+        <v>145.2715954612948</v>
       </c>
       <c r="J35">
         <v>180</v>
@@ -2853,28 +2841,28 @@
         <v>1</v>
       </c>
       <c r="L35">
-        <v>1.756036387465134</v>
+        <v>1.057798217128584</v>
       </c>
       <c r="M35">
-        <v>0.6097696916744146</v>
+        <v>0.7649337295269814</v>
       </c>
       <c r="N35">
-        <v>16.78832334705435</v>
+        <v>13.42643586024874</v>
       </c>
       <c r="O35">
         <v>1</v>
       </c>
       <c r="P35">
-        <v>116.7419784010775</v>
+        <v>118.8725284606768</v>
       </c>
       <c r="Q35">
-        <v>134.5247926826782</v>
+        <v>133.4338105602324</v>
       </c>
       <c r="R35">
-        <v>143.8823847420568</v>
+        <v>139.7029815486769</v>
       </c>
       <c r="S35" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="T35" t="b">
         <v>1</v>
@@ -2885,28 +2873,28 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C36" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D36" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E36" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="F36" t="s">
         <v>94</v>
       </c>
       <c r="G36">
-        <v>118.3261541474113</v>
+        <v>121.7547777991096</v>
       </c>
       <c r="H36">
-        <v>136.1089684290122</v>
+        <v>139.7035136206564</v>
       </c>
       <c r="I36">
-        <v>145.4665604883906</v>
+        <v>148.9202494422031</v>
       </c>
       <c r="J36">
         <v>180</v>
@@ -2915,28 +2903,28 @@
         <v>1</v>
       </c>
       <c r="L36">
-        <v>1.756036387465134</v>
+        <v>2.845453629675534</v>
       </c>
       <c r="M36">
-        <v>0.6097696916744146</v>
+        <v>0.6443182962905583</v>
       </c>
       <c r="N36">
-        <v>16.78832334705435</v>
+        <v>26.73295041172984</v>
       </c>
       <c r="O36">
         <v>1</v>
       </c>
       <c r="P36">
-        <v>125.3260445503233</v>
+        <v>111.8491029475612</v>
       </c>
       <c r="Q36">
-        <v>143.1088588319241</v>
+        <v>129.797838769108</v>
       </c>
       <c r="R36">
-        <v>152.4664508913026</v>
+        <v>139.0145745906547</v>
       </c>
       <c r="S36" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="T36" t="b">
         <v>1</v>
@@ -2947,28 +2935,28 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C37" t="s">
         <v>30</v>
       </c>
       <c r="D37" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E37" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F37" t="s">
         <v>95</v>
       </c>
       <c r="G37">
-        <v>127.8119691737715</v>
+        <v>122.3232802406482</v>
       </c>
       <c r="H37">
-        <v>148.2302906848501</v>
+        <v>141.8333083642319</v>
       </c>
       <c r="I37">
-        <v>160.2506121959288</v>
+        <v>153.0024475989267</v>
       </c>
       <c r="J37">
         <v>180</v>
@@ -2977,28 +2965,28 @@
         <v>1</v>
       </c>
       <c r="L37">
-        <v>2.306810552860246</v>
+        <v>2.113150583946663</v>
       </c>
       <c r="M37">
-        <v>0.4873754326977231</v>
+        <v>0.4717123540133343</v>
       </c>
       <c r="N37">
-        <v>19.440198958216</v>
+        <v>26.37275421739256</v>
       </c>
       <c r="O37">
         <v>1</v>
       </c>
       <c r="P37">
-        <v>137.2198581634844</v>
+        <v>113.7196049326193</v>
       </c>
       <c r="Q37">
-        <v>157.638179674563</v>
+        <v>133.229633056203</v>
       </c>
       <c r="R37">
-        <v>169.6585011856417</v>
+        <v>144.3987722908978</v>
       </c>
       <c r="S37" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="T37" t="b">
         <v>1</v>
@@ -3009,28 +2997,28 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C38" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D38" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E38" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F38" t="s">
         <v>96</v>
       </c>
       <c r="G38">
-        <v>131.61450838532</v>
+        <v>121.9728032321447</v>
       </c>
       <c r="H38">
-        <v>153.5836849393032</v>
+        <v>141.4875062070714</v>
       </c>
       <c r="I38">
-        <v>167.1646392710641</v>
+        <v>152.480209181998</v>
       </c>
       <c r="J38">
         <v>180</v>
@@ -3039,28 +3027,28 @@
         <v>1</v>
       </c>
       <c r="L38">
-        <v>2.494804901151978</v>
+        <v>3.686771208193226</v>
       </c>
       <c r="M38">
-        <v>0.445598910855116</v>
+        <v>0.5391535989758467</v>
       </c>
       <c r="N38">
-        <v>20.34535693147248</v>
+        <v>30.53056448142775</v>
       </c>
       <c r="O38">
         <v>1</v>
       </c>
       <c r="P38">
-        <v>138.4235623718171</v>
+        <v>121.9728032321447</v>
       </c>
       <c r="Q38">
-        <v>160.3927389258003</v>
+        <v>141.4875062070714</v>
       </c>
       <c r="R38">
-        <v>173.9736932575612</v>
+        <v>152.480209181998</v>
       </c>
       <c r="S38" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="T38" t="b">
         <v>1</v>
@@ -3074,55 +3062,55 @@
         <v>26</v>
       </c>
       <c r="C39" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D39" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="E39" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F39" t="s">
         <v>97</v>
       </c>
       <c r="G39">
-        <v>144.7152844569287</v>
+        <v>128.5010813119849</v>
       </c>
       <c r="H39">
-        <v>159.2765665564843</v>
+        <v>150.9255812506797</v>
       </c>
       <c r="I39">
-        <v>165.5457375449288</v>
+        <v>165.0843034115967</v>
       </c>
       <c r="J39">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="K39" t="b">
         <v>1</v>
       </c>
       <c r="L39">
-        <v>1.057798217128584</v>
+        <v>2.412427120788479</v>
       </c>
       <c r="M39">
-        <v>0.7649337295269814</v>
+        <v>0.4639050842692268</v>
       </c>
       <c r="N39">
-        <v>13.42643586024874</v>
+        <v>19.94872317416675</v>
       </c>
       <c r="O39">
         <v>1</v>
       </c>
       <c r="P39">
-        <v>154.1231734466416</v>
+        <v>118.9429141385297</v>
       </c>
       <c r="Q39">
-        <v>168.6844555461972</v>
+        <v>141.3674140772245</v>
       </c>
       <c r="R39">
-        <v>174.9536265346417</v>
+        <v>155.5261362381415</v>
       </c>
       <c r="S39" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="T39" t="b">
         <v>1</v>
@@ -3136,55 +3124,55 @@
         <v>21</v>
       </c>
       <c r="C40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D40" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E40" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F40" t="s">
         <v>98</v>
       </c>
       <c r="G40">
-        <v>134.0279476009105</v>
+        <v>148.9202494422031</v>
       </c>
       <c r="H40">
-        <v>150.6981730101556</v>
+        <v>169.9388243050544</v>
       </c>
       <c r="I40">
-        <v>159.1137317527341</v>
+        <v>182.0250658345724</v>
       </c>
       <c r="J40">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="K40" t="b">
         <v>1</v>
       </c>
       <c r="L40">
-        <v>1.304041604369885</v>
+        <v>4.375001305345046</v>
       </c>
       <c r="M40">
-        <v>0.6739895989075286</v>
+        <v>0.4531248368318692</v>
       </c>
       <c r="N40">
-        <v>20.52918936489361</v>
+        <v>33.63715866996027</v>
       </c>
       <c r="O40">
         <v>1</v>
       </c>
       <c r="P40">
-        <v>134.0279476009105</v>
+        <v>139.0145745906547</v>
       </c>
       <c r="Q40">
-        <v>150.6981730101556</v>
+        <v>160.033149453506</v>
       </c>
       <c r="R40">
-        <v>159.1137317527341</v>
+        <v>172.119390983024</v>
       </c>
       <c r="S40" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="T40" t="b">
         <v>1</v>
@@ -3195,58 +3183,58 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D41" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E41" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F41" t="s">
         <v>99</v>
       </c>
       <c r="G41">
-        <v>148.9566232377249</v>
+        <v>135.9024674104284</v>
       </c>
       <c r="H41">
-        <v>170.7192796901037</v>
+        <v>153.6852816920291</v>
       </c>
       <c r="I41">
-        <v>184.1410472535935</v>
+        <v>163.0428737514077</v>
       </c>
       <c r="J41">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="K41" t="b">
         <v>1</v>
       </c>
       <c r="L41">
-        <v>2.556464580723934</v>
+        <v>1.711944804864733</v>
       </c>
       <c r="M41">
-        <v>0.4318967598391258</v>
+        <v>0.6195678211411705</v>
       </c>
       <c r="N41">
-        <v>20.64223687015227</v>
+        <v>16.57603054194131</v>
       </c>
       <c r="O41">
         <v>1</v>
       </c>
       <c r="P41">
-        <v>155.765677224222</v>
+        <v>130.3533477946764</v>
       </c>
       <c r="Q41">
-        <v>177.5283336766009</v>
+        <v>148.1361620762771</v>
       </c>
       <c r="R41">
-        <v>190.9501012400906</v>
+        <v>157.4937541356557</v>
       </c>
       <c r="S41" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="T41" t="b">
         <v>1</v>
@@ -3257,58 +3245,58 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C42" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D42" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="E42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F42" t="s">
         <v>100</v>
       </c>
       <c r="G42">
-        <v>136.8786262223814</v>
+        <v>151.5851465350355</v>
       </c>
       <c r="H42">
-        <v>156.3933291973081</v>
+        <v>171.0951746586192</v>
       </c>
       <c r="I42">
-        <v>167.3860321722347</v>
+        <v>182.2643138933139</v>
       </c>
       <c r="J42">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="K42" t="b">
         <v>1</v>
       </c>
       <c r="L42">
-        <v>3.686771208193226</v>
+        <v>2.080451140464154</v>
       </c>
       <c r="M42">
-        <v>0.5391535989758467</v>
+        <v>0.4798872148839615</v>
       </c>
       <c r="N42">
-        <v>30.53056448142775</v>
+        <v>26.13659157001889</v>
       </c>
       <c r="O42">
         <v>1</v>
       </c>
       <c r="P42">
-        <v>124.2185433507283</v>
+        <v>142.9596148966238</v>
       </c>
       <c r="Q42">
-        <v>143.733246325655</v>
+        <v>162.4696430202075</v>
       </c>
       <c r="R42">
-        <v>154.7259493005816</v>
+        <v>173.6387822549022</v>
       </c>
       <c r="S42" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="T42" t="b">
         <v>1</v>
@@ -3319,28 +3307,28 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C43" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D43" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E43" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F43" t="s">
         <v>101</v>
       </c>
       <c r="G43">
-        <v>160.2506121959288</v>
+        <v>144.9916142556312</v>
       </c>
       <c r="H43">
-        <v>182.6751121346236</v>
+        <v>162.7564494107502</v>
       </c>
       <c r="I43">
-        <v>196.8338342955406</v>
+        <v>172.1349512325357</v>
       </c>
       <c r="J43">
         <v>240</v>
@@ -3349,28 +3337,28 @@
         <v>1</v>
       </c>
       <c r="L43">
-        <v>2.412427120788479</v>
+        <v>1.797687027182534</v>
       </c>
       <c r="M43">
-        <v>0.4639050842692268</v>
+        <v>0.6005139939594369</v>
       </c>
       <c r="N43">
-        <v>19.94872317416675</v>
+        <v>16.9888634642122</v>
       </c>
       <c r="O43">
         <v>1</v>
       </c>
       <c r="P43">
-        <v>169.6585011856417</v>
+        <v>136.2100749035394</v>
       </c>
       <c r="Q43">
-        <v>192.0830011243365</v>
+        <v>153.9749100586583</v>
       </c>
       <c r="R43">
-        <v>206.2417232852535</v>
+        <v>163.3534118804439</v>
       </c>
       <c r="S43" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="T43" t="b">
         <v>1</v>
@@ -3381,28 +3369,28 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C44" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D44" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E44" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F44" t="s">
         <v>102</v>
       </c>
       <c r="G44">
-        <v>158.3022598927292</v>
+        <v>152.9236501027265</v>
       </c>
       <c r="H44">
-        <v>178.1198665181702</v>
+        <v>166.8837186611424</v>
       </c>
       <c r="I44">
-        <v>189.5492509213889</v>
+        <v>171.884453886225</v>
       </c>
       <c r="J44">
         <v>240</v>
@@ -3411,28 +3399,28 @@
         <v>1</v>
       </c>
       <c r="L44">
-        <v>2.039725715171945</v>
+        <v>1.681614284379605</v>
       </c>
       <c r="M44">
-        <v>0.4900685712070139</v>
+        <v>0.7897982144525494</v>
       </c>
       <c r="N44">
-        <v>25.84246349846404</v>
+        <v>21.47950892254682</v>
       </c>
       <c r="O44">
         <v>1</v>
       </c>
       <c r="P44">
-        <v>158.3022598927292</v>
+        <v>152.9236501027265</v>
       </c>
       <c r="Q44">
-        <v>178.1198665181702</v>
+        <v>166.8837186611424</v>
       </c>
       <c r="R44">
-        <v>189.5492509213889</v>
+        <v>171.884453886225</v>
       </c>
       <c r="S44" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="T44" t="b">
         <v>1</v>
@@ -3443,28 +3431,28 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C45" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D45" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E45" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F45" t="s">
         <v>103</v>
       </c>
       <c r="G45">
-        <v>159.1137317527341</v>
+        <v>153.0024475989267</v>
       </c>
       <c r="H45">
-        <v>175.4237646988632</v>
+        <v>171.2698157913762</v>
       </c>
       <c r="I45">
-        <v>183.30857542277</v>
+        <v>181.4225173171591</v>
       </c>
       <c r="J45">
         <v>240</v>
@@ -3473,28 +3461,28 @@
         <v>1</v>
       </c>
       <c r="L45">
-        <v>1.42178203198294</v>
+        <v>1.684852321935074</v>
       </c>
       <c r="M45">
-        <v>0.6445544920042652</v>
+        <v>0.5787869195162316</v>
       </c>
       <c r="N45">
-        <v>21.37953689765456</v>
+        <v>23.2794889917533</v>
       </c>
       <c r="O45">
         <v>1</v>
       </c>
       <c r="P45">
-        <v>159.1137317527341</v>
+        <v>144.3987722908978</v>
       </c>
       <c r="Q45">
-        <v>175.4237646988632</v>
+        <v>162.6661404833473</v>
       </c>
       <c r="R45">
-        <v>183.30857542277</v>
+        <v>172.8188420091302</v>
       </c>
       <c r="S45" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="T45" t="b">
         <v>1</v>
@@ -3505,308 +3493,60 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C46" t="s">
         <v>29</v>
       </c>
       <c r="D46" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E46" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F46" t="s">
         <v>104</v>
       </c>
       <c r="G46">
-        <v>183.30857542277</v>
+        <v>145.2715954612948</v>
       </c>
       <c r="H46">
-        <v>202.8186035463537</v>
+        <v>163.0544097428956</v>
       </c>
       <c r="I46">
-        <v>213.9877427810484</v>
+        <v>172.4120018022741</v>
       </c>
       <c r="J46">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="K46" t="b">
         <v>1</v>
       </c>
       <c r="L46">
-        <v>2.080451140464154</v>
+        <v>1.698235657333516</v>
       </c>
       <c r="M46">
-        <v>0.4798872148839615</v>
+        <v>0.6226142983703299</v>
       </c>
       <c r="N46">
-        <v>26.13659157001889</v>
+        <v>16.51002353530952</v>
       </c>
       <c r="O46">
         <v>1</v>
       </c>
       <c r="P46">
-        <v>183.30857542277</v>
+        <v>139.7029815486769</v>
       </c>
       <c r="Q46">
-        <v>202.8186035463537</v>
+        <v>157.4857958302777</v>
       </c>
       <c r="R46">
-        <v>213.9877427810484</v>
+        <v>166.8433878896562</v>
       </c>
       <c r="S46" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="T46" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" t="s">
-        <v>28</v>
-      </c>
-      <c r="D47" t="s">
-        <v>39</v>
-      </c>
-      <c r="E47" t="s">
-        <v>58</v>
-      </c>
-      <c r="F47" t="s">
-        <v>105</v>
-      </c>
-      <c r="G47">
-        <v>152.9570077038221</v>
-      </c>
-      <c r="H47">
-        <v>170.0159568213422</v>
-      </c>
-      <c r="I47">
-        <v>178.1454059388622</v>
-      </c>
-      <c r="J47">
-        <v>240</v>
-      </c>
-      <c r="K47" t="b">
-        <v>1</v>
-      </c>
-      <c r="L47">
-        <v>3.136485864490634</v>
-      </c>
-      <c r="M47">
-        <v>0.6079392669386707</v>
-      </c>
-      <c r="N47">
-        <v>28.04663758277022</v>
-      </c>
-      <c r="O47">
-        <v>1</v>
-      </c>
-      <c r="P47">
-        <v>136.2775672011985</v>
-      </c>
-      <c r="Q47">
-        <v>153.3365163187186</v>
-      </c>
-      <c r="R47">
-        <v>161.4659654362386</v>
-      </c>
-      <c r="S47" t="s">
-        <v>110</v>
-      </c>
-      <c r="T47" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="s">
-        <v>20</v>
-      </c>
-      <c r="C48" t="s">
-        <v>28</v>
-      </c>
-      <c r="D48" t="s">
-        <v>40</v>
-      </c>
-      <c r="E48" t="s">
-        <v>59</v>
-      </c>
-      <c r="F48" t="s">
-        <v>106</v>
-      </c>
-      <c r="G48">
-        <v>167.3860321722347</v>
-      </c>
-      <c r="H48">
-        <v>181.3461007306506</v>
-      </c>
-      <c r="I48">
-        <v>186.3468359557332</v>
-      </c>
-      <c r="J48">
-        <v>240</v>
-      </c>
-      <c r="K48" t="b">
-        <v>1</v>
-      </c>
-      <c r="L48">
-        <v>1.681614284379605</v>
-      </c>
-      <c r="M48">
-        <v>0.7897982144525494</v>
-      </c>
-      <c r="N48">
-        <v>21.47950892254682</v>
-      </c>
-      <c r="O48">
-        <v>1</v>
-      </c>
-      <c r="P48">
-        <v>154.7259493005816</v>
-      </c>
-      <c r="Q48">
-        <v>168.6860178589975</v>
-      </c>
-      <c r="R48">
-        <v>173.6867530840801</v>
-      </c>
-      <c r="S48" t="s">
-        <v>109</v>
-      </c>
-      <c r="T48" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="s">
-        <v>26</v>
-      </c>
-      <c r="C49" t="s">
-        <v>30</v>
-      </c>
-      <c r="D49" t="s">
-        <v>41</v>
-      </c>
-      <c r="E49" t="s">
-        <v>56</v>
-      </c>
-      <c r="F49" t="s">
-        <v>107</v>
-      </c>
-      <c r="G49">
-        <v>165.5457375449288</v>
-      </c>
-      <c r="H49">
-        <v>185.4850795247659</v>
-      </c>
-      <c r="I49">
-        <v>197.3097548379364</v>
-      </c>
-      <c r="J49">
-        <v>240</v>
-      </c>
-      <c r="K49" t="b">
-        <v>1</v>
-      </c>
-      <c r="L49">
-        <v>2.014825572369929</v>
-      </c>
-      <c r="M49">
-        <v>0.5522609839177937</v>
-      </c>
-      <c r="N49">
-        <v>18.0343453484478</v>
-      </c>
-      <c r="O49">
-        <v>1</v>
-      </c>
-      <c r="P49">
-        <v>173.9736932575612</v>
-      </c>
-      <c r="Q49">
-        <v>193.9130352373983</v>
-      </c>
-      <c r="R49">
-        <v>205.7377105505688</v>
-      </c>
-      <c r="S49" t="s">
-        <v>111</v>
-      </c>
-      <c r="T49" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:20">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="s">
-        <v>22</v>
-      </c>
-      <c r="C50" t="s">
-        <v>30</v>
-      </c>
-      <c r="D50" t="s">
-        <v>44</v>
-      </c>
-      <c r="E50" t="s">
-        <v>57</v>
-      </c>
-      <c r="F50" t="s">
-        <v>108</v>
-      </c>
-      <c r="G50">
-        <v>178.9721734051776</v>
-      </c>
-      <c r="H50">
-        <v>196.7549876867784</v>
-      </c>
-      <c r="I50">
-        <v>206.1125797461569</v>
-      </c>
-      <c r="J50">
-        <v>300</v>
-      </c>
-      <c r="K50" t="b">
-        <v>1</v>
-      </c>
-      <c r="L50">
-        <v>1.698235657333516</v>
-      </c>
-      <c r="M50">
-        <v>0.6226142983703299</v>
-      </c>
-      <c r="N50">
-        <v>16.51002353530952</v>
-      </c>
-      <c r="O50">
-        <v>1</v>
-      </c>
-      <c r="P50">
-        <v>188.3800623948905</v>
-      </c>
-      <c r="Q50">
-        <v>206.1628766764913</v>
-      </c>
-      <c r="R50">
-        <v>215.5204687358698</v>
-      </c>
-      <c r="S50" t="s">
-        <v>111</v>
-      </c>
-      <c r="T50" t="b">
         <v>1</v>
       </c>
     </row>
